--- a/outputs/12864.xlsx
+++ b/outputs/12864.xlsx
@@ -771,7 +771,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.29"/>
@@ -793,7 +793,6 @@
         <f aca="false">INDEX(Sheet1!$B$2:$B$17,MATCH(A2,Sheet1!$D$2:$D$17,0))</f>
         <v>Monthly</v>
       </c>
-      <c r="C2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -803,7 +802,6 @@
         <f aca="false">INDEX(Sheet1!$B$2:$B$17,MATCH(A3,Sheet1!$D$2:$D$17,0))</f>
         <v>Monthly</v>
       </c>
-      <c r="C3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -813,7 +811,6 @@
         <f aca="false">INDEX(Sheet1!$B$2:$B$17,MATCH(A4,Sheet1!$D$2:$D$17,0))</f>
         <v>Daily</v>
       </c>
-      <c r="C4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
